--- a/E/SWACSP.xlsx
+++ b/E/SWACSP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t/>
   </si>
@@ -32,6 +32,18 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -424,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -494,6 +506,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/SWACSP.xlsx
+++ b/E/SWACSP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t/>
   </si>
@@ -44,6 +44,72 @@
   </si>
   <si>
     <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136102</t>
+  </si>
+  <si>
+    <t>IDM SOES STROBERI80G</t>
+  </si>
+  <si>
+    <t>20137880</t>
+  </si>
+  <si>
+    <t>IDM KACANG KRIUK 95G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20137876</t>
+  </si>
+  <si>
+    <t>IDM KACANG OVEN 95G</t>
+  </si>
+  <si>
+    <t>20038042</t>
+  </si>
+  <si>
+    <t>TOLL MILK CANDY 120</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20140881</t>
+  </si>
+  <si>
+    <t>TOLL CANDY BLUE 120G</t>
+  </si>
+  <si>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -436,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -526,6 +592,166 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/SWACSP.xlsx
+++ b/E/SWACSP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t/>
   </si>
@@ -502,17 +502,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,8 +532,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -548,11 +555,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -568,11 +575,11 @@
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -588,11 +595,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -608,11 +615,11 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -628,11 +635,11 @@
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -648,11 +655,11 @@
       <c r="E7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -668,11 +675,11 @@
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -688,11 +695,11 @@
       <c r="E9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -708,11 +715,11 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -728,11 +735,11 @@
       <c r="E11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -748,7 +755,7 @@
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>17</v>
       </c>
     </row>

--- a/E/SWACSP.xlsx
+++ b/E/SWACSP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t/>
   </si>
@@ -502,18 +502,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -532,14 +531,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -555,11 +548,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -575,11 +568,11 @@
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -595,11 +588,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -615,11 +608,11 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -635,11 +628,11 @@
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -655,11 +648,11 @@
       <c r="E7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -675,11 +668,11 @@
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -695,11 +688,11 @@
       <c r="E9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -715,11 +708,11 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -735,11 +728,11 @@
       <c r="E11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -755,7 +748,7 @@
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
     </row>

--- a/E/SWACSP.xlsx
+++ b/E/SWACSP.xlsx
@@ -11,66 +11,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141445</t>
-  </si>
-  <si>
-    <t>SR.KUE BOLU MINI ORG</t>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
   </si>
   <si>
     <t>SWACSP</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1H)</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136102</t>
+  </si>
+  <si>
+    <t>IDM SOES STROBERI80G</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136102</t>
-  </si>
-  <si>
-    <t>IDM SOES STROBERI80G</t>
   </si>
   <si>
     <t>20137880</t>
@@ -502,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -546,210 +537,170 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
